--- a/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
+++ b/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\بطاقات\futu card\WAAD FUTURE 2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\اسماء شركات الاسنان\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8627A31-AB33-4A0B-95FD-857D7DAFDC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11910"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,17 +20,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -577,7 +567,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
@@ -585,7 +575,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -605,14 +595,14 @@
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -977,7 +967,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1085,12 +1075,6 @@
     <xf numFmtId="1" fontId="2" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1136,55 +1120,52 @@
     <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1500,52 +1481,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I58"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I58"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.6328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="17.375" customWidth="1"/>
+    <col min="7" max="7" width="17.36328125" customWidth="1"/>
     <col min="8" max="8" width="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13.375" customWidth="1"/>
+    <col min="9" max="9" width="19.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="H1" s="25"/>
     </row>
-    <row r="2" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="61" t="s">
+    <row r="2" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C2" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-    </row>
-    <row r="3" spans="2:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="61"/>
-      <c r="D3" s="61"/>
-      <c r="E3" s="61"/>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="61"/>
-      <c r="I3" s="61"/>
-    </row>
-    <row r="4" spans="2:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+    </row>
+    <row r="3" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
+    </row>
+    <row r="4" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="2:9" ht="26.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="26.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
         <v>0</v>
       </c>
@@ -1571,14 +1552,17 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>1</v>
+      </c>
       <c r="B6" s="7">
         <v>21</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="60">
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1597,14 +1581,17 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2</v>
+      </c>
       <c r="B7" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="59"/>
+      <c r="D7" s="61"/>
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1621,14 +1608,17 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>3</v>
+      </c>
       <c r="B8" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="59"/>
+      <c r="D8" s="61"/>
       <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1645,14 +1635,17 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>4</v>
+      </c>
       <c r="B9" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="59"/>
+      <c r="D9" s="61"/>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1669,14 +1662,17 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="17.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>5</v>
+      </c>
       <c r="B10" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="59"/>
+      <c r="D10" s="61"/>
       <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1693,14 +1689,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>6</v>
+      </c>
       <c r="B11" s="9" t="s">
         <v>89</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="60"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="10" t="s">
         <v>12</v>
       </c>
@@ -1717,14 +1716,17 @@
         <v>101</v>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>7</v>
+      </c>
       <c r="B12" s="7">
         <v>22</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="60">
         <v>3</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -1743,14 +1745,17 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>8</v>
+      </c>
       <c r="B13" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="59"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1767,14 +1772,17 @@
         <v>102</v>
       </c>
     </row>
-    <row r="14" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>9</v>
+      </c>
       <c r="B14" s="11" t="s">
         <v>86</v>
       </c>
       <c r="C14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="59"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="13" t="s">
         <v>8</v>
       </c>
@@ -1791,14 +1799,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>10</v>
+      </c>
       <c r="B15" s="7">
         <v>23</v>
       </c>
       <c r="C15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="60">
         <v>3</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1817,14 +1828,17 @@
         <v>93</v>
       </c>
     </row>
-    <row r="16" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>11</v>
+      </c>
       <c r="B16" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="59"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
@@ -1841,14 +1855,17 @@
         <v>107</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>12</v>
+      </c>
       <c r="B17" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="60"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="10" t="s">
         <v>10</v>
       </c>
@@ -1865,14 +1882,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>13</v>
+      </c>
       <c r="B18" s="7">
         <v>24</v>
       </c>
       <c r="C18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="60">
         <v>7</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1891,14 +1911,17 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>14</v>
+      </c>
       <c r="B19" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="59"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1915,14 +1938,17 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>15</v>
+      </c>
       <c r="B20" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="59"/>
+      <c r="D20" s="61"/>
       <c r="E20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1939,14 +1965,17 @@
         <v>110</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>16</v>
+      </c>
       <c r="B21" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="59"/>
+      <c r="D21" s="61"/>
       <c r="E21" s="3" t="s">
         <v>10</v>
       </c>
@@ -1963,14 +1992,17 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>17</v>
+      </c>
       <c r="B22" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="59"/>
+      <c r="D22" s="61"/>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
@@ -1987,14 +2019,17 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>18</v>
+      </c>
       <c r="B23" s="2" t="s">
         <v>89</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="59"/>
+      <c r="D23" s="61"/>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
@@ -2011,14 +2046,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>19</v>
+      </c>
       <c r="B24" s="9" t="s">
         <v>90</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="60"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="10" t="s">
         <v>12</v>
       </c>
@@ -2035,14 +2073,17 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>20</v>
+      </c>
       <c r="B25" s="7">
         <v>25</v>
       </c>
       <c r="C25" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="60">
         <v>3</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -2061,14 +2102,17 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>21</v>
+      </c>
       <c r="B26" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="59"/>
+      <c r="D26" s="61"/>
       <c r="E26" s="3" t="s">
         <v>9</v>
       </c>
@@ -2085,14 +2129,17 @@
         <v>111</v>
       </c>
     </row>
-    <row r="27" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>22</v>
+      </c>
       <c r="B27" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="60"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="10" t="s">
         <v>10</v>
       </c>
@@ -2109,14 +2156,17 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>23</v>
+      </c>
       <c r="B28" s="7">
         <v>26</v>
       </c>
       <c r="C28" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="60">
         <v>4</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -2135,14 +2185,17 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>24</v>
+      </c>
       <c r="B29" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="59"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2159,14 +2212,17 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>25</v>
+      </c>
       <c r="B30" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="59"/>
+      <c r="D30" s="61"/>
       <c r="E30" s="3" t="s">
         <v>9</v>
       </c>
@@ -2183,14 +2239,17 @@
         <v>118</v>
       </c>
     </row>
-    <row r="31" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>26</v>
+      </c>
       <c r="B31" s="9" t="s">
         <v>87</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="60"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="10" t="s">
         <v>10</v>
       </c>
@@ -2207,14 +2266,17 @@
         <v>119</v>
       </c>
     </row>
-    <row r="32" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>27</v>
+      </c>
       <c r="B32" s="7">
         <v>27</v>
       </c>
       <c r="C32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D32" s="60">
         <v>3</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -2233,14 +2295,17 @@
         <v>104</v>
       </c>
     </row>
-    <row r="33" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>28</v>
+      </c>
       <c r="B33" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="59"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="3" t="s">
         <v>9</v>
       </c>
@@ -2257,14 +2322,17 @@
         <v>120</v>
       </c>
     </row>
-    <row r="34" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>29</v>
+      </c>
       <c r="B34" s="9" t="s">
         <v>86</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="60"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="10" t="s">
         <v>10</v>
       </c>
@@ -2281,14 +2349,17 @@
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>30</v>
+      </c>
       <c r="B35" s="7">
         <v>28</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="58">
+      <c r="D35" s="60">
         <v>2</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -2307,14 +2378,17 @@
         <v>105</v>
       </c>
     </row>
-    <row r="36" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>31</v>
+      </c>
       <c r="B36" s="9" t="s">
         <v>85</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="60"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="10" t="s">
         <v>10</v>
       </c>
@@ -2331,14 +2405,17 @@
         <v>122</v>
       </c>
     </row>
-    <row r="37" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>32</v>
+      </c>
       <c r="B37" s="7">
         <v>29</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="58">
+      <c r="D37" s="60">
         <v>6</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -2357,14 +2434,17 @@
         <v>106</v>
       </c>
     </row>
-    <row r="38" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>33</v>
+      </c>
       <c r="B38" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="59"/>
+      <c r="D38" s="61"/>
       <c r="E38" s="3" t="s">
         <v>5</v>
       </c>
@@ -2381,14 +2461,17 @@
         <v>123</v>
       </c>
     </row>
-    <row r="39" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>34</v>
+      </c>
       <c r="B39" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="59"/>
+      <c r="D39" s="61"/>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
@@ -2405,14 +2488,17 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>35</v>
+      </c>
       <c r="B40" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="59"/>
+      <c r="D40" s="61"/>
       <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
@@ -2429,14 +2515,17 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>36</v>
+      </c>
       <c r="B41" s="2" t="s">
         <v>88</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="59"/>
+      <c r="D41" s="61"/>
       <c r="E41" s="3" t="s">
         <v>59</v>
       </c>
@@ -2453,14 +2542,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="42" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>37</v>
+      </c>
       <c r="B42" s="11" t="s">
         <v>89</v>
       </c>
       <c r="C42" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D42" s="59"/>
+      <c r="D42" s="61"/>
       <c r="E42" s="12" t="s">
         <v>10</v>
       </c>
@@ -2477,88 +2569,100 @@
         <v>127</v>
       </c>
     </row>
-    <row r="43" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B43" s="39">
+    <row r="43" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>38</v>
+      </c>
+      <c r="B43" s="37">
         <v>30</v>
       </c>
-      <c r="C43" s="50" t="s">
+      <c r="C43" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="55">
+      <c r="D43" s="66">
         <v>3</v>
       </c>
-      <c r="E43" s="40" t="s">
+      <c r="E43" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F43" s="40" t="s">
+      <c r="F43" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="G43" s="46">
+      <c r="G43" s="44">
         <v>119710450349</v>
       </c>
-      <c r="H43" s="40" t="s">
+      <c r="H43" s="38" t="s">
         <v>132</v>
       </c>
       <c r="I43" s="28" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B44" s="37" t="s">
+    <row r="44" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>39</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C44" s="51" t="s">
+      <c r="C44" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="56"/>
-      <c r="E44" s="41" t="s">
+      <c r="D44" s="64"/>
+      <c r="E44" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="F44" s="41" t="s">
+      <c r="F44" s="39" t="s">
         <v>136</v>
       </c>
-      <c r="G44" s="47">
+      <c r="G44" s="45">
         <v>219840434667</v>
       </c>
-      <c r="H44" s="43">
+      <c r="H44" s="41">
         <v>30870</v>
       </c>
-      <c r="I44" s="44" t="s">
+      <c r="I44" s="42" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="45" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="38" t="s">
+    <row r="45" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>40</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="52" t="s">
+      <c r="C45" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="D45" s="57"/>
-      <c r="E45" s="42" t="s">
+      <c r="D45" s="67"/>
+      <c r="E45" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="F45" s="42" t="s">
+      <c r="F45" s="40" t="s">
         <v>137</v>
       </c>
-      <c r="G45" s="48">
+      <c r="G45" s="46">
         <v>220070187052</v>
       </c>
-      <c r="H45" s="45">
+      <c r="H45" s="43">
         <v>39209</v>
       </c>
-      <c r="I45" s="44" t="s">
+      <c r="I45" s="42" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="46" spans="2:9" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" ht="18.600000000000001" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>41</v>
+      </c>
       <c r="B46" s="7">
         <v>31</v>
       </c>
       <c r="C46" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D46" s="49">
+      <c r="D46" s="47">
         <v>1</v>
       </c>
       <c r="E46" s="8" t="s">
@@ -2577,268 +2681,310 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B47" s="39">
+    <row r="47" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>42</v>
+      </c>
+      <c r="B47" s="37">
         <v>32</v>
       </c>
-      <c r="C47" s="50" t="s">
+      <c r="C47" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="D47" s="54">
+      <c r="D47" s="65">
         <v>6</v>
       </c>
-      <c r="E47" s="40" t="s">
+      <c r="E47" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="F47" s="40" t="s">
+      <c r="F47" s="38" t="s">
         <v>146</v>
       </c>
-      <c r="G47" s="46">
+      <c r="G47" s="44">
         <v>119830073523</v>
       </c>
-      <c r="H47" s="40" t="s">
+      <c r="H47" s="38" t="s">
         <v>144</v>
       </c>
       <c r="I47" s="28" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="48" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B48" s="37" t="s">
+    <row r="48" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>43</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C48" s="51" t="s">
+      <c r="C48" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="54"/>
-      <c r="E48" s="51" t="s">
+      <c r="D48" s="65"/>
+      <c r="E48" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="51" t="s">
+      <c r="F48" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G48" s="47">
+      <c r="G48" s="45">
         <v>219880229429</v>
       </c>
-      <c r="H48" s="51" t="s">
+      <c r="H48" s="49" t="s">
         <v>148</v>
       </c>
-      <c r="I48" s="51" t="s">
+      <c r="I48" s="49" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="49" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B49" s="37" t="s">
+    <row r="49" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>44</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C49" s="51" t="s">
+      <c r="C49" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="D49" s="54"/>
-      <c r="E49" s="51" t="s">
+      <c r="D49" s="65"/>
+      <c r="E49" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="F49" s="51" t="s">
+      <c r="F49" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G49" s="47">
+      <c r="G49" s="45">
         <v>220140377341</v>
       </c>
-      <c r="H49" s="53">
+      <c r="H49" s="51">
         <v>41674</v>
       </c>
-      <c r="I49" s="51" t="s">
+      <c r="I49" s="49" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B50" s="37" t="s">
+    <row r="50" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>45</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C50" s="51" t="s">
+      <c r="C50" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="54"/>
-      <c r="E50" s="51" t="s">
+      <c r="D50" s="65"/>
+      <c r="E50" s="49" t="s">
         <v>153</v>
       </c>
-      <c r="F50" s="51" t="s">
+      <c r="F50" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="47">
+      <c r="G50" s="45">
         <v>120150788451</v>
       </c>
-      <c r="H50" s="51" t="s">
+      <c r="H50" s="49" t="s">
         <v>154</v>
       </c>
-      <c r="I50" s="51" t="s">
+      <c r="I50" s="49" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="51" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B51" s="37" t="s">
+    <row r="51" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>46</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C51" s="51" t="s">
+      <c r="C51" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="54"/>
-      <c r="E51" s="51" t="s">
+      <c r="D51" s="65"/>
+      <c r="E51" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="F51" s="51" t="s">
+      <c r="F51" s="49" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="47">
+      <c r="G51" s="45">
         <v>220170209777</v>
       </c>
-      <c r="H51" s="53">
+      <c r="H51" s="51">
         <v>43040</v>
       </c>
-      <c r="I51" s="51" t="s">
+      <c r="I51" s="49" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B52" s="62" t="s">
+    <row r="52" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>47</v>
+      </c>
+      <c r="B52" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C52" s="63" t="s">
+      <c r="C52" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="D52" s="54"/>
-      <c r="E52" s="63" t="s">
+      <c r="D52" s="65"/>
+      <c r="E52" s="52" t="s">
         <v>131</v>
       </c>
-      <c r="F52" s="63" t="s">
+      <c r="F52" s="52" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="64">
+      <c r="G52" s="53">
         <v>220210023000</v>
       </c>
-      <c r="H52" s="63" t="s">
+      <c r="H52" s="52" t="s">
         <v>159</v>
       </c>
-      <c r="I52" s="63" t="s">
+      <c r="I52" s="52" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="53" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B53" s="66"/>
-      <c r="C53" s="67" t="s">
+    <row r="53" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>48</v>
+      </c>
+      <c r="B53" s="55"/>
+      <c r="C53" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="56">
+      <c r="D53" s="64">
         <v>4</v>
       </c>
-      <c r="E53" s="67" t="s">
+      <c r="E53" s="56" t="s">
         <v>164</v>
       </c>
-      <c r="F53" s="68"/>
-      <c r="G53" s="69">
+      <c r="F53" s="57"/>
+      <c r="G53" s="58">
         <v>119910075623</v>
       </c>
-      <c r="H53" s="70" t="s">
+      <c r="H53" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="I53" s="67" t="s">
+      <c r="I53" s="56" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="54" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B54" s="66"/>
-      <c r="C54" s="51" t="s">
+    <row r="54" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>49</v>
+      </c>
+      <c r="B54" s="55"/>
+      <c r="C54" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="56"/>
-      <c r="E54" s="51" t="s">
+      <c r="D54" s="64"/>
+      <c r="E54" s="49" t="s">
         <v>130</v>
       </c>
-      <c r="F54" s="66"/>
-      <c r="G54" s="66">
+      <c r="F54" s="55"/>
+      <c r="G54" s="55">
         <v>219970382704</v>
       </c>
-      <c r="H54" s="51" t="s">
+      <c r="H54" s="49" t="s">
         <v>166</v>
       </c>
-      <c r="I54" s="51" t="s">
+      <c r="I54" s="49" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="55" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B55" s="66"/>
-      <c r="C55" s="51" t="s">
+    <row r="55" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>50</v>
+      </c>
+      <c r="B55" s="55"/>
+      <c r="C55" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="D55" s="56"/>
-      <c r="E55" s="51" t="s">
+      <c r="D55" s="64"/>
+      <c r="E55" s="49" t="s">
         <v>171</v>
       </c>
-      <c r="F55" s="66"/>
-      <c r="G55" s="66"/>
-      <c r="H55" s="65">
+      <c r="F55" s="55"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="54">
         <v>19360</v>
       </c>
-      <c r="I55" s="51" t="s">
+      <c r="I55" s="49" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="56" spans="2:9" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B56" s="66"/>
-      <c r="C56" s="51" t="s">
+    <row r="56" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>51</v>
+      </c>
+      <c r="B56" s="55"/>
+      <c r="C56" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="D56" s="56"/>
-      <c r="E56" s="51" t="s">
+      <c r="D56" s="64"/>
+      <c r="E56" s="49" t="s">
         <v>172</v>
       </c>
-      <c r="F56" s="66"/>
-      <c r="G56" s="66"/>
-      <c r="H56" s="65">
+      <c r="F56" s="55"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="54">
         <v>21916</v>
       </c>
-      <c r="I56" s="51" t="s">
+      <c r="I56" s="49" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="66"/>
-      <c r="C57" s="67" t="s">
+    <row r="57" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>52</v>
+      </c>
+      <c r="B57" s="55"/>
+      <c r="C57" s="56" t="s">
         <v>173</v>
       </c>
-      <c r="D57" s="68"/>
-      <c r="E57" s="67" t="s">
+      <c r="D57" s="57"/>
+      <c r="E57" s="56" t="s">
         <v>164</v>
       </c>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68" t="s">
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57" t="s">
         <v>174</v>
       </c>
-      <c r="I57" s="68" t="s">
+      <c r="I57" s="57" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="58" spans="2:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="B58" s="66"/>
-      <c r="C58" s="51" t="s">
+    <row r="58" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>53</v>
+      </c>
+      <c r="B58" s="55"/>
+      <c r="C58" s="49" t="s">
         <v>175</v>
       </c>
-      <c r="D58" s="66"/>
-      <c r="E58" s="51" t="s">
+      <c r="D58" s="55"/>
+      <c r="E58" s="49" t="s">
         <v>178</v>
       </c>
-      <c r="F58" s="66"/>
-      <c r="G58" s="66"/>
-      <c r="H58" s="66" t="s">
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55" t="s">
         <v>176</v>
       </c>
-      <c r="I58" s="66" t="s">
+      <c r="I58" s="55" t="s">
         <v>177</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="D47:D52"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="D18:D24"/>
@@ -2846,12 +2992,6 @@
     <mergeCell ref="C2:I3"/>
     <mergeCell ref="D6:D11"/>
     <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="D47:D52"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="D35:D36"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
+++ b/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\اسماء شركات الاسنان\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8627A31-AB33-4A0B-95FD-857D7DAFDC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E8E7AF-0DB9-4A1D-9938-ACFB2886BD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1144,18 +1144,6 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1166,6 +1154,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1503,24 +1503,24 @@
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="67" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="63"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
+      <c r="I2" s="67"/>
     </row>
     <row r="3" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="63"/>
-      <c r="I3" s="63"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
+      <c r="H3" s="67"/>
+      <c r="I3" s="67"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
@@ -1562,7 +1562,7 @@
       <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="60">
+      <c r="D6" s="64">
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1591,7 +1591,7 @@
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="61"/>
+      <c r="D7" s="65"/>
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="61"/>
+      <c r="D8" s="65"/>
       <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="61"/>
+      <c r="D9" s="65"/>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="61"/>
+      <c r="D10" s="65"/>
       <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1699,7 +1699,7 @@
       <c r="C11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="62"/>
+      <c r="D11" s="66"/>
       <c r="E11" s="10" t="s">
         <v>12</v>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="64">
         <v>3</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -1755,7 +1755,7 @@
       <c r="C13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="61"/>
+      <c r="D13" s="65"/>
       <c r="E13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1782,7 +1782,7 @@
       <c r="C14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="61"/>
+      <c r="D14" s="65"/>
       <c r="E14" s="13" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="C15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="60">
+      <c r="D15" s="64">
         <v>3</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1838,7 +1838,7 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="61"/>
+      <c r="D16" s="65"/>
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="62"/>
+      <c r="D17" s="66"/>
       <c r="E17" s="10" t="s">
         <v>10</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="C18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="60">
+      <c r="D18" s="64">
         <v>7</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1921,7 +1921,7 @@
       <c r="C19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="61"/>
+      <c r="D19" s="65"/>
       <c r="E19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1948,7 +1948,7 @@
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="61"/>
+      <c r="D20" s="65"/>
       <c r="E20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1975,7 +1975,7 @@
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="61"/>
+      <c r="D21" s="65"/>
       <c r="E21" s="3" t="s">
         <v>10</v>
       </c>
@@ -2002,7 +2002,7 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="61"/>
+      <c r="D22" s="65"/>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="61"/>
+      <c r="D23" s="65"/>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
@@ -2056,7 +2056,7 @@
       <c r="C24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="62"/>
+      <c r="D24" s="66"/>
       <c r="E24" s="10" t="s">
         <v>12</v>
       </c>
@@ -2083,7 +2083,7 @@
       <c r="C25" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="60">
+      <c r="D25" s="64">
         <v>3</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -2112,7 +2112,7 @@
       <c r="C26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="61"/>
+      <c r="D26" s="65"/>
       <c r="E26" s="3" t="s">
         <v>9</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="C27" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="62"/>
+      <c r="D27" s="66"/>
       <c r="E27" s="10" t="s">
         <v>10</v>
       </c>
@@ -2166,7 +2166,7 @@
       <c r="C28" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="60">
+      <c r="D28" s="64">
         <v>4</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -2195,7 +2195,7 @@
       <c r="C29" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="61"/>
+      <c r="D29" s="65"/>
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="C30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="61"/>
+      <c r="D30" s="65"/>
       <c r="E30" s="3" t="s">
         <v>9</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="C31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="62"/>
+      <c r="D31" s="66"/>
       <c r="E31" s="10" t="s">
         <v>10</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="C32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="60">
+      <c r="D32" s="64">
         <v>3</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -2305,7 +2305,7 @@
       <c r="C33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="61"/>
+      <c r="D33" s="65"/>
       <c r="E33" s="3" t="s">
         <v>9</v>
       </c>
@@ -2332,7 +2332,7 @@
       <c r="C34" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="62"/>
+      <c r="D34" s="66"/>
       <c r="E34" s="10" t="s">
         <v>10</v>
       </c>
@@ -2359,7 +2359,7 @@
       <c r="C35" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="60">
+      <c r="D35" s="64">
         <v>2</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -2388,7 +2388,7 @@
       <c r="C36" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="62"/>
+      <c r="D36" s="66"/>
       <c r="E36" s="10" t="s">
         <v>10</v>
       </c>
@@ -2415,7 +2415,7 @@
       <c r="C37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="60">
+      <c r="D37" s="64">
         <v>6</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -2444,7 +2444,7 @@
       <c r="C38" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="61"/>
+      <c r="D38" s="65"/>
       <c r="E38" s="3" t="s">
         <v>5</v>
       </c>
@@ -2471,7 +2471,7 @@
       <c r="C39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="61"/>
+      <c r="D39" s="65"/>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="C40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="61"/>
+      <c r="D40" s="65"/>
       <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="C41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="61"/>
+      <c r="D41" s="65"/>
       <c r="E41" s="3" t="s">
         <v>59</v>
       </c>
@@ -2552,7 +2552,7 @@
       <c r="C42" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D42" s="61"/>
+      <c r="D42" s="65"/>
       <c r="E42" s="12" t="s">
         <v>10</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="C43" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="66">
+      <c r="D43" s="62">
         <v>3</v>
       </c>
       <c r="E43" s="38" t="s">
@@ -2608,7 +2608,7 @@
       <c r="C44" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="64"/>
+      <c r="D44" s="60"/>
       <c r="E44" s="39" t="s">
         <v>130</v>
       </c>
@@ -2635,7 +2635,7 @@
       <c r="C45" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="D45" s="67"/>
+      <c r="D45" s="63"/>
       <c r="E45" s="40" t="s">
         <v>131</v>
       </c>
@@ -2691,7 +2691,7 @@
       <c r="C47" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="D47" s="65">
+      <c r="D47" s="61">
         <v>6</v>
       </c>
       <c r="E47" s="38" t="s">
@@ -2720,7 +2720,7 @@
       <c r="C48" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="65"/>
+      <c r="D48" s="61"/>
       <c r="E48" s="49" t="s">
         <v>5</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="C49" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="D49" s="65"/>
+      <c r="D49" s="61"/>
       <c r="E49" s="49" t="s">
         <v>131</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="C50" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="65"/>
+      <c r="D50" s="61"/>
       <c r="E50" s="49" t="s">
         <v>153</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="C51" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="65"/>
+      <c r="D51" s="61"/>
       <c r="E51" s="49" t="s">
         <v>131</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="C52" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="D52" s="65"/>
+      <c r="D52" s="61"/>
       <c r="E52" s="52" t="s">
         <v>131</v>
       </c>
@@ -2853,7 +2853,7 @@
       <c r="C53" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="64">
+      <c r="D53" s="60">
         <v>4</v>
       </c>
       <c r="E53" s="56" t="s">
@@ -2878,7 +2878,7 @@
       <c r="C54" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="64"/>
+      <c r="D54" s="60"/>
       <c r="E54" s="49" t="s">
         <v>130</v>
       </c>
@@ -2901,7 +2901,7 @@
       <c r="C55" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="D55" s="64"/>
+      <c r="D55" s="60"/>
       <c r="E55" s="49" t="s">
         <v>171</v>
       </c>
@@ -2922,7 +2922,7 @@
       <c r="C56" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="D56" s="64"/>
+      <c r="D56" s="60"/>
       <c r="E56" s="49" t="s">
         <v>172</v>
       </c>
@@ -2979,12 +2979,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="D47:D52"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="D18:D24"/>
@@ -2992,6 +2986,12 @@
     <mergeCell ref="C2:I3"/>
     <mergeCell ref="D6:D11"/>
     <mergeCell ref="D15:D17"/>
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="D47:D52"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="D35:D36"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
+++ b/اسماء شركات الاسنان/قائمة فيوتشر المدمجة.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Omar\waad_temp_website\اسماء شركات الاسنان\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E8E7AF-0DB9-4A1D-9938-ACFB2886BD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EEE809B-ACC5-4EC7-A0B1-08F8FFE317AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1144,6 +1144,18 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1154,18 +1166,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1503,24 +1503,24 @@
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C2" s="67" t="s">
+      <c r="C2" s="63" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
-      <c r="I2" s="67"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
     </row>
     <row r="3" spans="1:9" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+      <c r="H3" s="63"/>
+      <c r="I3" s="63"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E4" s="1"/>
@@ -1562,7 +1562,7 @@
       <c r="C6" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="64">
+      <c r="D6" s="60">
         <v>6</v>
       </c>
       <c r="E6" s="8" t="s">
@@ -1591,7 +1591,7 @@
       <c r="C7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="65"/>
+      <c r="D7" s="61"/>
       <c r="E7" s="3" t="s">
         <v>9</v>
       </c>
@@ -1618,7 +1618,7 @@
       <c r="C8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D8" s="65"/>
+      <c r="D8" s="61"/>
       <c r="E8" s="3" t="s">
         <v>10</v>
       </c>
@@ -1645,7 +1645,7 @@
       <c r="C9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="65"/>
+      <c r="D9" s="61"/>
       <c r="E9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1672,7 +1672,7 @@
       <c r="C10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="65"/>
+      <c r="D10" s="61"/>
       <c r="E10" s="3" t="s">
         <v>12</v>
       </c>
@@ -1699,7 +1699,7 @@
       <c r="C11" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="66"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="10" t="s">
         <v>12</v>
       </c>
@@ -1726,7 +1726,7 @@
       <c r="C12" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="D12" s="64">
+      <c r="D12" s="60">
         <v>3</v>
       </c>
       <c r="E12" s="8" t="s">
@@ -1755,7 +1755,7 @@
       <c r="C13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="65"/>
+      <c r="D13" s="61"/>
       <c r="E13" s="3" t="s">
         <v>5</v>
       </c>
@@ -1782,7 +1782,7 @@
       <c r="C14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="65"/>
+      <c r="D14" s="61"/>
       <c r="E14" s="13" t="s">
         <v>8</v>
       </c>
@@ -1809,7 +1809,7 @@
       <c r="C15" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="60">
         <v>3</v>
       </c>
       <c r="E15" s="8" t="s">
@@ -1838,7 +1838,7 @@
       <c r="C16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="65"/>
+      <c r="D16" s="61"/>
       <c r="E16" s="3" t="s">
         <v>9</v>
       </c>
@@ -1865,7 +1865,7 @@
       <c r="C17" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D17" s="66"/>
+      <c r="D17" s="62"/>
       <c r="E17" s="10" t="s">
         <v>10</v>
       </c>
@@ -1892,7 +1892,7 @@
       <c r="C18" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="60">
         <v>7</v>
       </c>
       <c r="E18" s="8" t="s">
@@ -1921,7 +1921,7 @@
       <c r="C19" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="65"/>
+      <c r="D19" s="61"/>
       <c r="E19" s="3" t="s">
         <v>5</v>
       </c>
@@ -1948,7 +1948,7 @@
       <c r="C20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D20" s="65"/>
+      <c r="D20" s="61"/>
       <c r="E20" s="3" t="s">
         <v>9</v>
       </c>
@@ -1975,7 +1975,7 @@
       <c r="C21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D21" s="65"/>
+      <c r="D21" s="61"/>
       <c r="E21" s="3" t="s">
         <v>10</v>
       </c>
@@ -2002,7 +2002,7 @@
       <c r="C22" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D22" s="65"/>
+      <c r="D22" s="61"/>
       <c r="E22" s="3" t="s">
         <v>11</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="C23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="65"/>
+      <c r="D23" s="61"/>
       <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
@@ -2056,7 +2056,7 @@
       <c r="C24" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="D24" s="66"/>
+      <c r="D24" s="62"/>
       <c r="E24" s="10" t="s">
         <v>12</v>
       </c>
@@ -2083,7 +2083,7 @@
       <c r="C25" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D25" s="64">
+      <c r="D25" s="60">
         <v>3</v>
       </c>
       <c r="E25" s="8" t="s">
@@ -2112,7 +2112,7 @@
       <c r="C26" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="65"/>
+      <c r="D26" s="61"/>
       <c r="E26" s="3" t="s">
         <v>9</v>
       </c>
@@ -2139,7 +2139,7 @@
       <c r="C27" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D27" s="66"/>
+      <c r="D27" s="62"/>
       <c r="E27" s="10" t="s">
         <v>10</v>
       </c>
@@ -2166,7 +2166,7 @@
       <c r="C28" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="D28" s="64">
+      <c r="D28" s="60">
         <v>4</v>
       </c>
       <c r="E28" s="8" t="s">
@@ -2195,7 +2195,7 @@
       <c r="C29" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D29" s="65"/>
+      <c r="D29" s="61"/>
       <c r="E29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2222,7 +2222,7 @@
       <c r="C30" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="65"/>
+      <c r="D30" s="61"/>
       <c r="E30" s="3" t="s">
         <v>9</v>
       </c>
@@ -2249,7 +2249,7 @@
       <c r="C31" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="66"/>
+      <c r="D31" s="62"/>
       <c r="E31" s="10" t="s">
         <v>10</v>
       </c>
@@ -2276,7 +2276,7 @@
       <c r="C32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="64">
+      <c r="D32" s="60">
         <v>3</v>
       </c>
       <c r="E32" s="8" t="s">
@@ -2305,7 +2305,7 @@
       <c r="C33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="65"/>
+      <c r="D33" s="61"/>
       <c r="E33" s="3" t="s">
         <v>9</v>
       </c>
@@ -2332,7 +2332,7 @@
       <c r="C34" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="D34" s="66"/>
+      <c r="D34" s="62"/>
       <c r="E34" s="10" t="s">
         <v>10</v>
       </c>
@@ -2359,7 +2359,7 @@
       <c r="C35" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="D35" s="64">
+      <c r="D35" s="60">
         <v>2</v>
       </c>
       <c r="E35" s="8" t="s">
@@ -2388,7 +2388,7 @@
       <c r="C36" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="D36" s="66"/>
+      <c r="D36" s="62"/>
       <c r="E36" s="10" t="s">
         <v>10</v>
       </c>
@@ -2415,7 +2415,7 @@
       <c r="C37" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="D37" s="64">
+      <c r="D37" s="60">
         <v>6</v>
       </c>
       <c r="E37" s="8" t="s">
@@ -2444,7 +2444,7 @@
       <c r="C38" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D38" s="65"/>
+      <c r="D38" s="61"/>
       <c r="E38" s="3" t="s">
         <v>5</v>
       </c>
@@ -2471,7 +2471,7 @@
       <c r="C39" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D39" s="65"/>
+      <c r="D39" s="61"/>
       <c r="E39" s="3" t="s">
         <v>11</v>
       </c>
@@ -2498,7 +2498,7 @@
       <c r="C40" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D40" s="65"/>
+      <c r="D40" s="61"/>
       <c r="E40" s="3" t="s">
         <v>12</v>
       </c>
@@ -2525,7 +2525,7 @@
       <c r="C41" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D41" s="65"/>
+      <c r="D41" s="61"/>
       <c r="E41" s="3" t="s">
         <v>59</v>
       </c>
@@ -2552,7 +2552,7 @@
       <c r="C42" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="D42" s="65"/>
+      <c r="D42" s="61"/>
       <c r="E42" s="12" t="s">
         <v>10</v>
       </c>
@@ -2579,7 +2579,7 @@
       <c r="C43" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="D43" s="62">
+      <c r="D43" s="66">
         <v>3</v>
       </c>
       <c r="E43" s="38" t="s">
@@ -2608,7 +2608,7 @@
       <c r="C44" s="49" t="s">
         <v>129</v>
       </c>
-      <c r="D44" s="60"/>
+      <c r="D44" s="64"/>
       <c r="E44" s="39" t="s">
         <v>130</v>
       </c>
@@ -2635,7 +2635,7 @@
       <c r="C45" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="D45" s="63"/>
+      <c r="D45" s="67"/>
       <c r="E45" s="40" t="s">
         <v>131</v>
       </c>
@@ -2691,7 +2691,7 @@
       <c r="C47" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="D47" s="61">
+      <c r="D47" s="65">
         <v>6</v>
       </c>
       <c r="E47" s="38" t="s">
@@ -2720,7 +2720,7 @@
       <c r="C48" s="49" t="s">
         <v>147</v>
       </c>
-      <c r="D48" s="61"/>
+      <c r="D48" s="65"/>
       <c r="E48" s="49" t="s">
         <v>5</v>
       </c>
@@ -2747,7 +2747,7 @@
       <c r="C49" s="49" t="s">
         <v>150</v>
       </c>
-      <c r="D49" s="61"/>
+      <c r="D49" s="65"/>
       <c r="E49" s="49" t="s">
         <v>131</v>
       </c>
@@ -2774,7 +2774,7 @@
       <c r="C50" s="49" t="s">
         <v>152</v>
       </c>
-      <c r="D50" s="61"/>
+      <c r="D50" s="65"/>
       <c r="E50" s="49" t="s">
         <v>153</v>
       </c>
@@ -2801,7 +2801,7 @@
       <c r="C51" s="49" t="s">
         <v>157</v>
       </c>
-      <c r="D51" s="61"/>
+      <c r="D51" s="65"/>
       <c r="E51" s="49" t="s">
         <v>131</v>
       </c>
@@ -2828,7 +2828,7 @@
       <c r="C52" s="52" t="s">
         <v>158</v>
       </c>
-      <c r="D52" s="61"/>
+      <c r="D52" s="65"/>
       <c r="E52" s="52" t="s">
         <v>131</v>
       </c>
@@ -2849,11 +2849,13 @@
       <c r="A53">
         <v>48</v>
       </c>
-      <c r="B53" s="55"/>
+      <c r="B53" s="55">
+        <v>33</v>
+      </c>
       <c r="C53" s="56" t="s">
         <v>162</v>
       </c>
-      <c r="D53" s="60">
+      <c r="D53" s="64">
         <v>4</v>
       </c>
       <c r="E53" s="56" t="s">
@@ -2878,7 +2880,7 @@
       <c r="C54" s="49" t="s">
         <v>163</v>
       </c>
-      <c r="D54" s="60"/>
+      <c r="D54" s="64"/>
       <c r="E54" s="49" t="s">
         <v>130</v>
       </c>
@@ -2901,7 +2903,7 @@
       <c r="C55" s="49" t="s">
         <v>169</v>
       </c>
-      <c r="D55" s="60"/>
+      <c r="D55" s="64"/>
       <c r="E55" s="49" t="s">
         <v>171</v>
       </c>
@@ -2922,7 +2924,7 @@
       <c r="C56" s="49" t="s">
         <v>170</v>
       </c>
-      <c r="D56" s="60"/>
+      <c r="D56" s="64"/>
       <c r="E56" s="49" t="s">
         <v>172</v>
       </c>
@@ -2979,6 +2981,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="D53:D56"/>
+    <mergeCell ref="D47:D52"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="D28:D31"/>
+    <mergeCell ref="D35:D36"/>
     <mergeCell ref="D25:D27"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="D18:D24"/>
@@ -2986,12 +2994,6 @@
     <mergeCell ref="C2:I3"/>
     <mergeCell ref="D6:D11"/>
     <mergeCell ref="D15:D17"/>
-    <mergeCell ref="D53:D56"/>
-    <mergeCell ref="D47:D52"/>
-    <mergeCell ref="D43:D45"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="D28:D31"/>
-    <mergeCell ref="D35:D36"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
